--- a/Avwap_Tarama_220526.xlsx
+++ b/Avwap_Tarama_220526.xlsx
@@ -229,6 +229,9 @@
     <t>ATEKS</t>
   </si>
   <si>
+    <t>ATLAS</t>
+  </si>
+  <si>
     <t>ATSYH</t>
   </si>
   <si>
@@ -275,9 +278,6 @@
   </si>
   <si>
     <t>BALSU</t>
-  </si>
-  <si>
-    <t>BANVT</t>
   </si>
   <si>
     <t>BARMA</t>
@@ -4969,37 +4969,37 @@
         <v>585</v>
       </c>
       <c r="C58">
-        <v>70</v>
+        <v>7.94</v>
       </c>
       <c r="D58">
-        <v>3.17</v>
+        <v>2.85</v>
       </c>
       <c r="E58">
-        <v>37.19</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="F58">
-        <v>53.91</v>
+        <v>43.1</v>
       </c>
       <c r="G58">
-        <v>-0.44</v>
+        <v>-0.15</v>
       </c>
       <c r="J58">
-        <v>61.82</v>
+        <v>8.74</v>
       </c>
       <c r="K58">
-        <v>60.37</v>
+        <v>8.4</v>
       </c>
       <c r="L58">
-        <v>75.76000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M58">
-        <v>62.64</v>
+        <v>8.69</v>
       </c>
       <c r="N58">
-        <v>60.48</v>
+        <v>8.42</v>
       </c>
       <c r="O58">
-        <v>62.12</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="59" spans="1:15">
@@ -5010,37 +5010,37 @@
         <v>585</v>
       </c>
       <c r="C59">
-        <v>11.68</v>
+        <v>70</v>
       </c>
       <c r="D59">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="E59">
-        <v>-27.68</v>
+        <v>37.19</v>
       </c>
       <c r="F59">
-        <v>41.14</v>
+        <v>53.91</v>
       </c>
       <c r="G59">
-        <v>-0.22</v>
+        <v>-0.44</v>
       </c>
       <c r="J59">
-        <v>12.09</v>
+        <v>61.82</v>
       </c>
       <c r="K59">
-        <v>12.99</v>
+        <v>60.37</v>
       </c>
       <c r="L59">
-        <v>13.19</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="M59">
-        <v>12.02</v>
+        <v>62.64</v>
       </c>
       <c r="N59">
-        <v>12.31</v>
+        <v>60.48</v>
       </c>
       <c r="O59">
-        <v>12.76</v>
+        <v>62.12</v>
       </c>
     </row>
     <row r="60" spans="1:15">
@@ -5051,43 +5051,37 @@
         <v>585</v>
       </c>
       <c r="C60">
-        <v>38.58</v>
+        <v>11.68</v>
       </c>
       <c r="D60">
-        <v>5.41</v>
+        <v>3.18</v>
       </c>
       <c r="E60">
-        <v>3.88</v>
+        <v>-27.68</v>
       </c>
       <c r="F60">
-        <v>49.17</v>
+        <v>41.14</v>
       </c>
       <c r="G60">
-        <v>-0.29</v>
-      </c>
-      <c r="H60" t="s">
-        <v>606</v>
-      </c>
-      <c r="I60" t="s">
-        <v>692</v>
+        <v>-0.22</v>
       </c>
       <c r="J60">
-        <v>38.72</v>
+        <v>12.09</v>
       </c>
       <c r="K60">
-        <v>38.1</v>
+        <v>12.99</v>
       </c>
       <c r="L60">
-        <v>38.39</v>
+        <v>13.19</v>
       </c>
       <c r="M60">
-        <v>38.64</v>
+        <v>12.02</v>
       </c>
       <c r="N60">
-        <v>38.39</v>
+        <v>12.31</v>
       </c>
       <c r="O60">
-        <v>38.06</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="61" spans="1:15">
@@ -5098,37 +5092,43 @@
         <v>585</v>
       </c>
       <c r="C61">
-        <v>4.42</v>
+        <v>38.58</v>
       </c>
       <c r="D61">
-        <v>3.51</v>
+        <v>5.41</v>
       </c>
       <c r="E61">
-        <v>18.28</v>
+        <v>3.88</v>
       </c>
       <c r="F61">
-        <v>45.9</v>
+        <v>49.17</v>
       </c>
       <c r="G61">
-        <v>-0.05</v>
+        <v>-0.29</v>
+      </c>
+      <c r="H61" t="s">
+        <v>606</v>
+      </c>
+      <c r="I61" t="s">
+        <v>692</v>
       </c>
       <c r="J61">
-        <v>4.71</v>
+        <v>38.72</v>
       </c>
       <c r="K61">
-        <v>4.72</v>
+        <v>38.1</v>
       </c>
       <c r="L61">
-        <v>4.88</v>
+        <v>38.39</v>
       </c>
       <c r="M61">
-        <v>4.7</v>
+        <v>38.64</v>
       </c>
       <c r="N61">
-        <v>4.72</v>
+        <v>38.39</v>
       </c>
       <c r="O61">
-        <v>4.76</v>
+        <v>38.06</v>
       </c>
     </row>
     <row r="62" spans="1:15">
@@ -5139,43 +5139,37 @@
         <v>585</v>
       </c>
       <c r="C62">
-        <v>61.2</v>
+        <v>4.42</v>
       </c>
       <c r="D62">
-        <v>2.51</v>
+        <v>3.51</v>
       </c>
       <c r="E62">
-        <v>92.48999999999999</v>
+        <v>18.28</v>
       </c>
       <c r="F62">
-        <v>51.69</v>
+        <v>45.9</v>
       </c>
       <c r="G62">
-        <v>-0.59</v>
-      </c>
-      <c r="H62" t="s">
-        <v>597</v>
-      </c>
-      <c r="I62" t="s">
-        <v>694</v>
+        <v>-0.05</v>
       </c>
       <c r="J62">
-        <v>55.48</v>
+        <v>4.71</v>
       </c>
       <c r="K62">
-        <v>55.17</v>
+        <v>4.72</v>
       </c>
       <c r="L62">
-        <v>63.2</v>
+        <v>4.88</v>
       </c>
       <c r="M62">
-        <v>55.37</v>
+        <v>4.7</v>
       </c>
       <c r="N62">
-        <v>55.18</v>
+        <v>4.72</v>
       </c>
       <c r="O62">
-        <v>56.42</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="63" spans="1:15">
@@ -5186,37 +5180,43 @@
         <v>585</v>
       </c>
       <c r="C63">
-        <v>522</v>
+        <v>61.2</v>
       </c>
       <c r="D63">
-        <v>4.82</v>
+        <v>2.51</v>
       </c>
       <c r="E63">
-        <v>-24.89</v>
+        <v>92.48999999999999</v>
       </c>
       <c r="F63">
-        <v>24.75</v>
+        <v>51.69</v>
       </c>
       <c r="G63">
-        <v>-39.11</v>
+        <v>-0.59</v>
+      </c>
+      <c r="H63" t="s">
+        <v>597</v>
+      </c>
+      <c r="I63" t="s">
+        <v>694</v>
       </c>
       <c r="J63">
-        <v>714.4400000000001</v>
+        <v>55.48</v>
       </c>
       <c r="K63">
-        <v>788.5599999999999</v>
+        <v>55.17</v>
       </c>
       <c r="L63">
-        <v>695.51</v>
+        <v>63.2</v>
       </c>
       <c r="M63">
-        <v>708.87</v>
+        <v>55.37</v>
       </c>
       <c r="N63">
-        <v>740.1900000000001</v>
+        <v>55.18</v>
       </c>
       <c r="O63">
-        <v>807.65</v>
+        <v>56.42</v>
       </c>
     </row>
     <row r="64" spans="1:15">
@@ -5227,37 +5227,37 @@
         <v>585</v>
       </c>
       <c r="C64">
-        <v>24.62</v>
+        <v>522</v>
       </c>
       <c r="D64">
-        <v>2.16</v>
+        <v>4.82</v>
       </c>
       <c r="E64">
-        <v>64.19</v>
+        <v>-24.89</v>
       </c>
       <c r="F64">
-        <v>32.33</v>
+        <v>24.75</v>
       </c>
       <c r="G64">
-        <v>-0.45</v>
+        <v>-39.11</v>
       </c>
       <c r="J64">
-        <v>27.76</v>
+        <v>714.4400000000001</v>
       </c>
       <c r="K64">
-        <v>28.52</v>
+        <v>788.5599999999999</v>
       </c>
       <c r="L64">
-        <v>29.01</v>
+        <v>695.51</v>
       </c>
       <c r="M64">
-        <v>26.65</v>
+        <v>708.87</v>
       </c>
       <c r="N64">
-        <v>28.36</v>
+        <v>740.1900000000001</v>
       </c>
       <c r="O64">
-        <v>28.6</v>
+        <v>807.65</v>
       </c>
     </row>
     <row r="65" spans="1:15">
@@ -5268,37 +5268,37 @@
         <v>585</v>
       </c>
       <c r="C65">
-        <v>32.9</v>
+        <v>24.62</v>
       </c>
       <c r="D65">
-        <v>5.11</v>
+        <v>2.16</v>
       </c>
       <c r="E65">
-        <v>7.32</v>
+        <v>64.19</v>
       </c>
       <c r="F65">
-        <v>45.89</v>
+        <v>32.33</v>
       </c>
       <c r="G65">
-        <v>-0.49</v>
+        <v>-0.45</v>
       </c>
       <c r="J65">
-        <v>33.82</v>
+        <v>27.76</v>
       </c>
       <c r="K65">
-        <v>34.62</v>
+        <v>28.52</v>
       </c>
       <c r="L65">
-        <v>35.35</v>
+        <v>29.01</v>
       </c>
       <c r="M65">
-        <v>34.22</v>
+        <v>26.65</v>
       </c>
       <c r="N65">
-        <v>34.73</v>
+        <v>28.36</v>
       </c>
       <c r="O65">
-        <v>34.91</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="66" spans="1:15">
@@ -5309,43 +5309,37 @@
         <v>585</v>
       </c>
       <c r="C66">
-        <v>31.3</v>
+        <v>32.9</v>
       </c>
       <c r="D66">
-        <v>4.33</v>
+        <v>5.11</v>
       </c>
       <c r="E66">
-        <v>-49.11</v>
+        <v>7.32</v>
       </c>
       <c r="F66">
-        <v>57.62</v>
+        <v>45.89</v>
       </c>
       <c r="G66">
-        <v>-0</v>
-      </c>
-      <c r="H66" t="s">
-        <v>607</v>
-      </c>
-      <c r="I66" t="s">
-        <v>691</v>
+        <v>-0.49</v>
       </c>
       <c r="J66">
-        <v>26.99</v>
+        <v>33.82</v>
       </c>
       <c r="K66">
-        <v>29.53</v>
+        <v>34.62</v>
       </c>
       <c r="L66">
-        <v>30.81</v>
+        <v>35.35</v>
       </c>
       <c r="M66">
-        <v>27.19</v>
+        <v>34.22</v>
       </c>
       <c r="N66">
-        <v>29.68</v>
+        <v>34.73</v>
       </c>
       <c r="O66">
-        <v>30.56</v>
+        <v>34.91</v>
       </c>
     </row>
     <row r="67" spans="1:15">
@@ -5356,43 +5350,43 @@
         <v>585</v>
       </c>
       <c r="C67">
-        <v>250</v>
+        <v>31.3</v>
       </c>
       <c r="D67">
-        <v>0.89</v>
+        <v>4.33</v>
       </c>
       <c r="E67">
-        <v>160.08</v>
+        <v>-49.11</v>
       </c>
       <c r="F67">
-        <v>36.34</v>
+        <v>57.62</v>
       </c>
       <c r="G67">
-        <v>-4.98</v>
+        <v>-0</v>
       </c>
       <c r="H67" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="I67" t="s">
         <v>691</v>
       </c>
       <c r="J67">
-        <v>255.9</v>
+        <v>26.99</v>
       </c>
       <c r="K67">
-        <v>276.3</v>
+        <v>29.53</v>
       </c>
       <c r="L67">
-        <v>275.73</v>
+        <v>30.81</v>
       </c>
       <c r="M67">
-        <v>248.38</v>
+        <v>27.19</v>
       </c>
       <c r="N67">
-        <v>264.15</v>
+        <v>29.68</v>
       </c>
       <c r="O67">
-        <v>276.64</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="68" spans="1:15">
@@ -5403,37 +5397,43 @@
         <v>585</v>
       </c>
       <c r="C68">
-        <v>4.52</v>
+        <v>250</v>
       </c>
       <c r="D68">
-        <v>4.63</v>
+        <v>0.89</v>
       </c>
       <c r="E68">
-        <v>-12.62</v>
+        <v>160.08</v>
       </c>
       <c r="F68">
-        <v>48.06</v>
+        <v>36.34</v>
       </c>
       <c r="G68">
-        <v>-0.05</v>
+        <v>-4.98</v>
+      </c>
+      <c r="H68" t="s">
+        <v>608</v>
+      </c>
+      <c r="I68" t="s">
+        <v>691</v>
       </c>
       <c r="J68">
-        <v>4.56</v>
+        <v>255.9</v>
       </c>
       <c r="K68">
-        <v>4.55</v>
+        <v>276.3</v>
       </c>
       <c r="L68">
-        <v>4.67</v>
+        <v>275.73</v>
       </c>
       <c r="M68">
-        <v>4.55</v>
+        <v>248.38</v>
       </c>
       <c r="N68">
-        <v>4.54</v>
+        <v>264.15</v>
       </c>
       <c r="O68">
-        <v>4.58</v>
+        <v>276.64</v>
       </c>
     </row>
     <row r="69" spans="1:15">
@@ -5444,37 +5444,37 @@
         <v>585</v>
       </c>
       <c r="C69">
-        <v>28.52</v>
+        <v>4.52</v>
       </c>
       <c r="D69">
-        <v>2.52</v>
+        <v>4.63</v>
       </c>
       <c r="E69">
-        <v>1.4</v>
+        <v>-12.62</v>
       </c>
       <c r="F69">
-        <v>32.83</v>
+        <v>48.06</v>
       </c>
       <c r="G69">
-        <v>-0.76</v>
+        <v>-0.05</v>
       </c>
       <c r="J69">
-        <v>35.45</v>
+        <v>4.56</v>
       </c>
       <c r="K69">
-        <v>35.05</v>
+        <v>4.55</v>
       </c>
       <c r="L69">
-        <v>33.6</v>
+        <v>4.67</v>
       </c>
       <c r="M69">
-        <v>35.24</v>
+        <v>4.55</v>
       </c>
       <c r="N69">
-        <v>35.41</v>
+        <v>4.54</v>
       </c>
       <c r="O69">
-        <v>34.35</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="70" spans="1:15">
@@ -5485,37 +5485,37 @@
         <v>585</v>
       </c>
       <c r="C70">
-        <v>109</v>
+        <v>28.52</v>
       </c>
       <c r="D70">
-        <v>4.51</v>
+        <v>2.52</v>
       </c>
       <c r="E70">
-        <v>91.12</v>
+        <v>1.4</v>
       </c>
       <c r="F70">
-        <v>39.17</v>
+        <v>32.83</v>
       </c>
       <c r="G70">
-        <v>-1.12</v>
+        <v>-0.76</v>
       </c>
       <c r="J70">
-        <v>124.44</v>
+        <v>35.45</v>
       </c>
       <c r="K70">
-        <v>127.52</v>
+        <v>35.05</v>
       </c>
       <c r="L70">
-        <v>119.23</v>
+        <v>33.6</v>
       </c>
       <c r="M70">
-        <v>123.29</v>
+        <v>35.24</v>
       </c>
       <c r="N70">
-        <v>124.46</v>
+        <v>35.41</v>
       </c>
       <c r="O70">
-        <v>120.07</v>
+        <v>34.35</v>
       </c>
     </row>
     <row r="71" spans="1:15">
@@ -5526,43 +5526,37 @@
         <v>585</v>
       </c>
       <c r="C71">
-        <v>46.02</v>
+        <v>109</v>
       </c>
       <c r="D71">
-        <v>1.46</v>
+        <v>4.51</v>
       </c>
       <c r="E71">
-        <v>-48.91</v>
+        <v>91.12</v>
       </c>
       <c r="F71">
-        <v>51.29</v>
+        <v>39.17</v>
       </c>
       <c r="G71">
-        <v>-0.09</v>
-      </c>
-      <c r="H71" t="s">
-        <v>609</v>
-      </c>
-      <c r="I71" t="s">
-        <v>694</v>
+        <v>-1.12</v>
       </c>
       <c r="J71">
-        <v>44.14</v>
+        <v>124.44</v>
       </c>
       <c r="K71">
-        <v>46.72</v>
+        <v>127.52</v>
       </c>
       <c r="L71">
-        <v>45.58</v>
+        <v>119.23</v>
       </c>
       <c r="M71">
-        <v>44.01</v>
+        <v>123.29</v>
       </c>
       <c r="N71">
-        <v>44.35</v>
+        <v>124.46</v>
       </c>
       <c r="O71">
-        <v>47.22</v>
+        <v>120.07</v>
       </c>
     </row>
     <row r="72" spans="1:15">
@@ -5573,37 +5567,43 @@
         <v>585</v>
       </c>
       <c r="C72">
-        <v>73</v>
+        <v>46.02</v>
       </c>
       <c r="D72">
-        <v>9.609999999999999</v>
+        <v>1.46</v>
       </c>
       <c r="E72">
-        <v>32.71</v>
+        <v>-48.91</v>
       </c>
       <c r="F72">
-        <v>38.32</v>
+        <v>51.29</v>
       </c>
       <c r="G72">
-        <v>-0.22</v>
+        <v>-0.09</v>
+      </c>
+      <c r="H72" t="s">
+        <v>609</v>
+      </c>
+      <c r="I72" t="s">
+        <v>694</v>
       </c>
       <c r="J72">
-        <v>91.81999999999999</v>
+        <v>44.14</v>
       </c>
       <c r="K72">
-        <v>87.58</v>
+        <v>46.72</v>
       </c>
       <c r="L72">
-        <v>73.94</v>
+        <v>45.58</v>
       </c>
       <c r="M72">
-        <v>94.70999999999999</v>
+        <v>44.01</v>
       </c>
       <c r="N72">
-        <v>89.12</v>
+        <v>44.35</v>
       </c>
       <c r="O72">
-        <v>74.28</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="73" spans="1:15">
@@ -5614,37 +5614,37 @@
         <v>585</v>
       </c>
       <c r="C73">
-        <v>13.26</v>
+        <v>73</v>
       </c>
       <c r="D73">
-        <v>1.84</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="E73">
-        <v>152.52</v>
+        <v>32.71</v>
       </c>
       <c r="F73">
-        <v>34.94</v>
+        <v>38.32</v>
       </c>
       <c r="G73">
-        <v>-0.18</v>
+        <v>-0.22</v>
       </c>
       <c r="J73">
-        <v>15.81</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="K73">
-        <v>15.43</v>
+        <v>87.58</v>
       </c>
       <c r="L73">
-        <v>14.71</v>
+        <v>73.94</v>
       </c>
       <c r="M73">
-        <v>16.08</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="N73">
-        <v>15.53</v>
+        <v>89.12</v>
       </c>
       <c r="O73">
-        <v>14.67</v>
+        <v>74.28</v>
       </c>
     </row>
     <row r="74" spans="1:15">
@@ -5655,37 +5655,37 @@
         <v>585</v>
       </c>
       <c r="C74">
-        <v>150.3</v>
+        <v>13.26</v>
       </c>
       <c r="D74">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="E74">
-        <v>99.3</v>
+        <v>152.52</v>
       </c>
       <c r="F74">
-        <v>39.2</v>
+        <v>34.94</v>
       </c>
       <c r="G74">
-        <v>-1.45</v>
+        <v>-0.18</v>
       </c>
       <c r="J74">
-        <v>161.4</v>
+        <v>15.81</v>
       </c>
       <c r="K74">
-        <v>158.44</v>
+        <v>15.43</v>
       </c>
       <c r="L74">
-        <v>160.26</v>
+        <v>14.71</v>
       </c>
       <c r="M74">
-        <v>163.47</v>
+        <v>16.08</v>
       </c>
       <c r="N74">
-        <v>158</v>
+        <v>15.53</v>
       </c>
       <c r="O74">
-        <v>158.63</v>
+        <v>14.67</v>
       </c>
     </row>
     <row r="75" spans="1:15">
